--- a/output/材料成型技术_2025-2026-1/06_达成度报告分析底表.xlsx
+++ b/output/材料成型技术_2025-2026-1/06_达成度报告分析底表.xlsx
@@ -8,6 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析底表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课程目标汇总表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学生个体达成度表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未达成学生清单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="达成度分布统计表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图表数据表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -697,4 +702,4586 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>课程目标编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>课程目标描述</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>综合平均达成值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>合格阈值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>是否达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2-1：能够合理应用数学、自然科学和工程科学的基本原理，识别和判断机械工程领域复杂工程问题的关键环节和参数。</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6728666666666666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4-2：能够根据实验方案构建实验系统，安全使用操作实验设备，合理确定测试参数，正确开展实验，科学采集和整理实验数据。</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6692666666666666</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>学号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>课程目标编号</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>过程性成绩</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>期末成绩</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>综合达成度</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>是否达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>202121010429</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>李源鑫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>202201130622</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>吴志浩</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>202208020306</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>冯杰</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>202221010201</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>杨硕</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>202221010209</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>左超</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3840000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8640000000000001</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>202221010213</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>王贺兵</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>202221010215</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>刘子豪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>202221010301</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>张伦嘉</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>202221010303</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>刘晨阳</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>202221010312</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>张海天</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>202221010414</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>吴楚云</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>202221010514</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>周雨豪</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>202306150210</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刘星宇</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>202321010101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>蔡宗旭</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8480000000000001</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>202321010103</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>冯创毅</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>202321010106</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>林炬宏</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6880000000000001</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>202321010107</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>刘锦亿</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8320000000000001</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>202321010110</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>邵杨</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>202321010111</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>石权</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>202321010115</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>田武杰</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.6759999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>202321010116</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>王锦</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>202321010117</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>谢文俊</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6679999999999999</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>202321010118</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>徐凤铎</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.6960000000000001</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>202321010119</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>杨俊熙</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>202321010121</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>游展</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8440000000000001</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>202321010123</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>袁智勇</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>202321010214</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>罗玉辉</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>202321010221</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>王品一</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>202321010223</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>王琦</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>202321010224</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>王晟</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>202321010228</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>杨超</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.6759999999999999</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>202321010229</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>袁海</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>202321010231</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>赵少雄</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3080000000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>202321010301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>陈冠杰</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>202321010302</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>成晗</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6679999999999999</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>202321010303</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>邓宇杰</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>202321010314</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>吕金城</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.3840000000000001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9120000000000001</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>202321010316</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>粟永总</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>202321010322</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>徐维阳</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4919999999999999</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>202321010326</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>张顺翔</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>202321010328</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>周洛</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>202321010329</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>周兴诚</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6200000000000001</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>202321010401</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>陈小康</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>202321010416</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>彭真</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>202321010417</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>邱富霖</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3840000000000001</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>202321010419</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>田志</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>202321010426</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>张永江</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>202321010427</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>张桀</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>202321010428</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>周宇航</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>202321010430</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>朱俞凭</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>202321010431</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>胥博</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>202321010503</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>邓浪</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.6880000000000001</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>202321010504</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>邓云珑</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6839999999999999</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>202321010508</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>黎济玮</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>202321010509</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>李欣</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>202321010514</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>刘鑫</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>202321010516</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>毛宇</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>202321010518</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>王佳瑜</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.6160000000000001</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>202321010528</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>张智钦</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>202321010529</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>赵焕州</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>202121010429</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>李源鑫</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.6120000000000001</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>202201130622</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>吴志浩</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.6439999999999999</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>202208020306</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>冯杰</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>202221010201</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>杨硕</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>202221010209</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>左超</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.8560000000000001</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>202221010213</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>王贺兵</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.6560000000000001</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>202221010215</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>刘子豪</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>202221010301</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>张伦嘉</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>202221010303</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>刘晨阳</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>202221010312</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>张海天</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>202221010414</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>吴楚云</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.6839999999999999</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>202221010514</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>周雨豪</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.6799999999999999</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>202306150210</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>刘星宇</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>202321010101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>蔡宗旭</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.8160000000000001</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>202321010103</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>冯创毅</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>202321010106</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>林炬宏</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.5840000000000001</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>202321010107</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>刘锦亿</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.4919999999999999</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.8759999999999999</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>202321010110</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>邵杨</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>202321010111</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>石权</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>202321010115</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>田武杰</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>202321010116</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>王锦</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>202321010117</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>谢文俊</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>202321010118</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>徐凤铎</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>202321010119</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>杨俊熙</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>202321010121</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>游展</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>202321010123</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>袁智勇</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>202321010214</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>罗玉辉</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.4319999999999999</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>202321010221</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>王品一</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>202321010223</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>王琦</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>202321010224</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>王晟</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>202321010228</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>杨超</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>202321010229</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>袁海</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>202321010231</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>赵少雄</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.3080000000000001</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.4919999999999999</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>202321010301</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>陈冠杰</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>202321010302</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>成晗</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>202321010303</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>邓宇杰</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>202321010314</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>吕金城</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>202321010316</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>粟永总</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>202321010322</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>徐维阳</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.4919999999999999</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.8759999999999999</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>202321010326</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>张顺翔</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>202321010328</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>周洛</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>202321010329</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>周兴诚</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.5720000000000001</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>202321010401</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>陈小康</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>202321010416</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>彭真</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>202321010417</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>邱富霖</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>202321010419</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>田志</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>202321010426</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>张永江</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.6960000000000001</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>202321010427</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>张桀</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>202321010428</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>周宇航</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.3760000000000001</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>202321010430</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>朱俞凭</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>202321010431</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>胥博</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>202321010503</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>邓浪</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>202321010504</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>邓云珑</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.8240000000000001</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>202321010508</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>黎济玮</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>202321010509</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>李欣</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>202321010514</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>刘鑫</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8240000000000001</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>202321010516</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>毛宇</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>202321010518</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>王佳瑜</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>202321010528</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>张智钦</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.6719999999999999</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>达成</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>202321010529</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>赵焕州</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>未达成</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>课程目标编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学号</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>综合达成度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>202221010201</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>杨硕</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>202221010301</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>张伦嘉</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.576</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>202321010103</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>冯创毅</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>202321010214</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>罗玉辉</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.536</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>202321010221</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>王品一</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.452</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>202321010303</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>邓宇杰</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>202321010419</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>田志</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.336</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>202321010431</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>胥博</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.416</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>202221010201</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>杨硕</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>202321010103</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>冯创毅</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>202321010106</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>林炬宏</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5840000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>202321010214</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>罗玉辉</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4319999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>202321010221</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>王品一</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.472</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>202321010303</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>邓宇杰</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.384</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>202321010329</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>周兴诚</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5720000000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>202321010419</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>田志</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.344</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>202321010431</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>胥博</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>202321010529</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>赵焕州</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>课程目标编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>达成度区间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>&lt;0.60</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.60-0.70</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3833333333333334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.70-0.80</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.80-0.90</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&gt;=0.90</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>&lt;0.60</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.60-0.70</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.70-0.80</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>21</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.80-0.90</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>&gt;=0.90</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>课程目标编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>综合平均达成值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>未达成人数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>0.60-0.70</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>0.70-0.80</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>0.80-0.90</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>&lt;0.60</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>&gt;=0.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程目标1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.6728666666666666</v>
+      </c>
+      <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程目标2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6692666666666666</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/材料成型技术_2025-2026-1/06_达成度报告分析底表.xlsx
+++ b/output/材料成型技术_2025-2026-1/06_达成度报告分析底表.xlsx
@@ -568,11 +568,11 @@
         <v>0.6728666666666666</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -598,22 +598,22 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>达成情况偏弱</t>
+          <t>基本达标</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>目标达成不足，需重点改进</t>
+          <t>虽达到标准，但学生掌握不均衡</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>课程目标1综合平均达成值为0.673，未达到预设达标阈值0.70。低分段占比为51.7%，高分段占比为15.0%。</t>
+          <t>课程目标1综合平均达成值为0.673，达到预设达标阈值0.60。低分段占比为51.7%，高分段占比为15.0%。</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>后续教学中应强化重点难点内容讲解，并加强针对性训练与过程指导。</t>
+          <t>后续教学中应加强分层指导和过程反馈，缩小学生之间的达成差异。</t>
         </is>
       </c>
     </row>
@@ -650,11 +650,11 @@
         <v>0.6692666666666666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>未达标</t>
+          <t>达标</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -680,22 +680,22 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>达成情况偏弱</t>
+          <t>基本达标</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>目标达成不足，需重点改进</t>
+          <t>虽达到标准，但学生掌握不均衡</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>课程目标2综合平均达成值为0.669，未达到预设达标阈值0.70。低分段占比为48.3%，高分段占比为16.7%。</t>
+          <t>课程目标2综合平均达成值为0.669，达到预设达标阈值0.60。低分段占比为48.3%，高分段占比为16.7%。</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>后续教学中应强化重点难点内容讲解，并加强针对性训练与过程指导。</t>
+          <t>后续教学中应加强分层指导和过程反馈，缩小学生之间的达成差异。</t>
         </is>
       </c>
     </row>
